--- a/upload/orgao2026.xlsx
+++ b/upload/orgao2026.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20400" windowHeight="10695"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="8400"/>
   </bookViews>
   <sheets>
     <sheet name="visaogeral" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="151">
   <si>
     <t>Ano de Exercício</t>
   </si>
@@ -112,24 +112,6 @@
   </si>
   <si>
     <t>EGE-SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTAO</t>
-  </si>
-  <si>
-    <t>EMATER</t>
-  </si>
-  <si>
-    <t>EMPRESA DE ASSISTENCIA TECNICA E EXTENSAO RURAL DO ESTADO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>EPAMIG</t>
-  </si>
-  <si>
-    <t>EMPRESA DE PESQUISA AGROPECUARIA DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>EMC</t>
-  </si>
-  <si>
-    <t>EMPRESA MINEIRA DE COMUNICACAO</t>
   </si>
   <si>
     <t>ESP MG</t>
@@ -861,7 +843,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I76"/>
+  <dimension ref="A1:I73"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
@@ -917,16 +899,16 @@
         <v>10</v>
       </c>
       <c r="E2" s="6">
-        <v>514070266.26999998</v>
+        <v>540750049.59000003</v>
       </c>
       <c r="F2" s="6">
-        <v>383116076.66000003</v>
+        <v>384098792.83999997</v>
       </c>
       <c r="G2" s="6">
-        <v>365361783.47000003</v>
+        <v>366105819.32999998</v>
       </c>
       <c r="H2" s="6">
-        <v>383116076.66000003</v>
+        <v>384098792.83999997</v>
       </c>
       <c r="I2" s="7">
         <v>187674481.12</v>
@@ -978,13 +960,13 @@
         <v>3937101.41</v>
       </c>
       <c r="F4" s="6">
-        <v>1683364.47</v>
+        <v>1685298.07</v>
       </c>
       <c r="G4" s="6">
-        <v>1554216.32</v>
+        <v>1556128.26</v>
       </c>
       <c r="H4" s="6">
-        <v>1683364.47</v>
+        <v>1685298.07</v>
       </c>
       <c r="I4" s="7">
         <v>685196.49</v>
@@ -1033,16 +1015,16 @@
         <v>18</v>
       </c>
       <c r="E6" s="6">
-        <v>25128488.149999999</v>
+        <v>25128623.149999999</v>
       </c>
       <c r="F6" s="6">
-        <v>13537981.66</v>
+        <v>14426659.390000001</v>
       </c>
       <c r="G6" s="6">
-        <v>12533557.74</v>
+        <v>12548609.83</v>
       </c>
       <c r="H6" s="6">
-        <v>13537981.66</v>
+        <v>14426659.390000001</v>
       </c>
       <c r="I6" s="7">
         <v>2159796.8199999998</v>
@@ -1062,16 +1044,16 @@
         <v>20</v>
       </c>
       <c r="E7" s="6">
-        <v>29046645.109999999</v>
+        <v>29046728.489999998</v>
       </c>
       <c r="F7" s="6">
-        <v>28659281.68</v>
+        <v>28672743.059999999</v>
       </c>
       <c r="G7" s="6">
-        <v>28518667.66</v>
+        <v>28518776.25</v>
       </c>
       <c r="H7" s="6">
-        <v>28659281.68</v>
+        <v>28672743.059999999</v>
       </c>
       <c r="I7" s="7">
         <v>1316450.02</v>
@@ -1091,19 +1073,19 @@
         <v>22</v>
       </c>
       <c r="E8" s="6">
-        <v>862947452.44000006</v>
+        <v>863315329</v>
       </c>
       <c r="F8" s="6">
-        <v>836388913.13999999</v>
+        <v>838153265.67999995</v>
       </c>
       <c r="G8" s="6">
-        <v>834818516.61000001</v>
+        <v>834865165.63999999</v>
       </c>
       <c r="H8" s="6">
-        <v>836388913.13999999</v>
+        <v>838153265.67999995</v>
       </c>
       <c r="I8" s="7">
-        <v>36138381.960000001</v>
+        <v>36154674.079999998</v>
       </c>
     </row>
     <row r="9" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -1120,19 +1102,19 @@
         <v>24</v>
       </c>
       <c r="E9" s="6">
-        <v>830849455.10000002</v>
+        <v>855888368.28999996</v>
       </c>
       <c r="F9" s="6">
-        <v>393755367.43000001</v>
+        <v>399327372.89999998</v>
       </c>
       <c r="G9" s="6">
-        <v>372863327.19</v>
+        <v>374727646.85000002</v>
       </c>
       <c r="H9" s="6">
-        <v>393755367.43000001</v>
+        <v>399327372.89999998</v>
       </c>
       <c r="I9" s="7">
-        <v>254848857.25</v>
+        <v>256020269.97</v>
       </c>
     </row>
     <row r="10" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -1149,13 +1131,13 @@
         <v>26</v>
       </c>
       <c r="E10" s="6">
-        <v>30411118.300000001</v>
+        <v>34254327</v>
       </c>
       <c r="F10" s="6">
         <v>28486969.609999999</v>
       </c>
       <c r="G10" s="6">
-        <v>19441641.190000001</v>
+        <v>19442488.550000001</v>
       </c>
       <c r="H10" s="6">
         <v>28486969.609999999</v>
@@ -1225,7 +1207,7 @@
         <v>2026</v>
       </c>
       <c r="B13" s="4">
-        <v>3041</v>
+        <v>1541</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>31</v>
@@ -1234,25 +1216,27 @@
         <v>32</v>
       </c>
       <c r="E13" s="6">
-        <v>113201966.42</v>
+        <v>10485267.49</v>
       </c>
       <c r="F13" s="6">
-        <v>113201966.42</v>
+        <v>9072029.2799999993</v>
       </c>
       <c r="G13" s="6">
-        <v>113201966.42</v>
+        <v>8866928.0500000007</v>
       </c>
       <c r="H13" s="6">
-        <v>113201966.42</v>
-      </c>
-      <c r="I13" s="7"/>
+        <v>9072029.2799999993</v>
+      </c>
+      <c r="I13" s="7">
+        <v>1171305.47</v>
+      </c>
     </row>
     <row r="14" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="4">
         <v>2026</v>
       </c>
       <c r="B14" s="4">
-        <v>3051</v>
+        <v>2321</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>33</v>
@@ -1261,25 +1245,27 @@
         <v>34</v>
       </c>
       <c r="E14" s="6">
-        <v>45052077.520000003</v>
+        <v>180136537.49000001</v>
       </c>
       <c r="F14" s="6">
-        <v>45052077.520000003</v>
+        <v>145509863.28999999</v>
       </c>
       <c r="G14" s="6">
-        <v>45052077.520000003</v>
+        <v>136104860.59</v>
       </c>
       <c r="H14" s="6">
-        <v>45052077.520000003</v>
-      </c>
-      <c r="I14" s="7"/>
+        <v>145509863.28999999</v>
+      </c>
+      <c r="I14" s="7">
+        <v>26745380.5</v>
+      </c>
     </row>
     <row r="15" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="4">
         <v>2026</v>
       </c>
       <c r="B15" s="4">
-        <v>3151</v>
+        <v>2181</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>35</v>
@@ -1288,25 +1274,27 @@
         <v>36</v>
       </c>
       <c r="E15" s="6">
-        <v>9639005.1199999992</v>
+        <v>30747920.5</v>
       </c>
       <c r="F15" s="6">
-        <v>9639005.1199999992</v>
+        <v>22347482.800000001</v>
       </c>
       <c r="G15" s="6">
-        <v>9639005.1199999992</v>
+        <v>21821703.43</v>
       </c>
       <c r="H15" s="6">
-        <v>9639005.1199999992</v>
-      </c>
-      <c r="I15" s="7"/>
+        <v>22347482.800000001</v>
+      </c>
+      <c r="I15" s="7">
+        <v>2463402.91</v>
+      </c>
     </row>
     <row r="16" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="4">
         <v>2026</v>
       </c>
       <c r="B16" s="4">
-        <v>1541</v>
+        <v>2071</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>37</v>
@@ -1315,19 +1303,19 @@
         <v>38</v>
       </c>
       <c r="E16" s="6">
-        <v>10416820.49</v>
+        <v>264457039.31</v>
       </c>
       <c r="F16" s="6">
-        <v>9071623.4800000004</v>
+        <v>202771442.52000001</v>
       </c>
       <c r="G16" s="6">
-        <v>8866928.0500000007</v>
+        <v>195257599.62</v>
       </c>
       <c r="H16" s="6">
-        <v>9071623.4800000004</v>
+        <v>202771442.52000001</v>
       </c>
       <c r="I16" s="7">
-        <v>1171305.47</v>
+        <v>6540600.3499999996</v>
       </c>
     </row>
     <row r="17" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -1335,7 +1323,7 @@
         <v>2026</v>
       </c>
       <c r="B17" s="4">
-        <v>2321</v>
+        <v>2171</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>39</v>
@@ -1344,19 +1332,19 @@
         <v>40</v>
       </c>
       <c r="E17" s="6">
-        <v>179506609.28</v>
+        <v>1983915.82</v>
       </c>
       <c r="F17" s="6">
-        <v>144540649.19</v>
+        <v>1908956.6</v>
       </c>
       <c r="G17" s="6">
-        <v>133630046.31</v>
+        <v>1826994.99</v>
       </c>
       <c r="H17" s="6">
-        <v>144540649.19</v>
+        <v>1908956.6</v>
       </c>
       <c r="I17" s="7">
-        <v>26744040.379999999</v>
+        <v>111797.23</v>
       </c>
     </row>
     <row r="18" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -1364,7 +1352,7 @@
         <v>2026</v>
       </c>
       <c r="B18" s="4">
-        <v>2181</v>
+        <v>2281</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>41</v>
@@ -1373,19 +1361,19 @@
         <v>42</v>
       </c>
       <c r="E18" s="6">
-        <v>30747920.5</v>
+        <v>3347499.61</v>
       </c>
       <c r="F18" s="6">
-        <v>22341650.91</v>
+        <v>2750555.28</v>
       </c>
       <c r="G18" s="6">
-        <v>21816095.969999999</v>
+        <v>2499719.59</v>
       </c>
       <c r="H18" s="6">
-        <v>22341650.91</v>
+        <v>2750555.28</v>
       </c>
       <c r="I18" s="7">
-        <v>2463402.91</v>
+        <v>263905.44</v>
       </c>
     </row>
     <row r="19" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -1393,7 +1381,7 @@
         <v>2026</v>
       </c>
       <c r="B19" s="4">
-        <v>2071</v>
+        <v>2161</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>43</v>
@@ -1402,19 +1390,19 @@
         <v>44</v>
       </c>
       <c r="E19" s="6">
-        <v>264377195.88</v>
+        <v>2379404.08</v>
       </c>
       <c r="F19" s="6">
-        <v>201836659.09</v>
+        <v>2244486.7200000002</v>
       </c>
       <c r="G19" s="6">
-        <v>195206035.53</v>
+        <v>2196094.87</v>
       </c>
       <c r="H19" s="6">
-        <v>201836659.09</v>
+        <v>2244486.7200000002</v>
       </c>
       <c r="I19" s="7">
-        <v>6540600.3499999996</v>
+        <v>177706.84</v>
       </c>
     </row>
     <row r="20" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -1422,7 +1410,7 @@
         <v>2026</v>
       </c>
       <c r="B20" s="4">
-        <v>2171</v>
+        <v>2091</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>45</v>
@@ -1431,19 +1419,19 @@
         <v>46</v>
       </c>
       <c r="E20" s="6">
-        <v>1962037.18</v>
+        <v>28509020.510000002</v>
       </c>
       <c r="F20" s="6">
-        <v>1780269.96</v>
+        <v>27662195.219999999</v>
       </c>
       <c r="G20" s="6">
-        <v>1718725.41</v>
+        <v>26582239.879999999</v>
       </c>
       <c r="H20" s="6">
-        <v>1780269.96</v>
+        <v>27662195.219999999</v>
       </c>
       <c r="I20" s="7">
-        <v>111797.23</v>
+        <v>1012619.95</v>
       </c>
     </row>
     <row r="21" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -1451,7 +1439,7 @@
         <v>2026</v>
       </c>
       <c r="B21" s="4">
-        <v>2281</v>
+        <v>2261</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>47</v>
@@ -1460,19 +1448,19 @@
         <v>48</v>
       </c>
       <c r="E21" s="6">
-        <v>3347499.61</v>
+        <v>217426879.84</v>
       </c>
       <c r="F21" s="6">
-        <v>2750555.22</v>
+        <v>128187574.08</v>
       </c>
       <c r="G21" s="6">
-        <v>2499624.59</v>
+        <v>119685675.98</v>
       </c>
       <c r="H21" s="6">
-        <v>2750555.22</v>
+        <v>128187574.08</v>
       </c>
       <c r="I21" s="7">
-        <v>263905.44</v>
+        <v>140223800.16999999</v>
       </c>
     </row>
     <row r="22" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -1480,7 +1468,7 @@
         <v>2026</v>
       </c>
       <c r="B22" s="4">
-        <v>2161</v>
+        <v>2151</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>49</v>
@@ -1489,19 +1477,19 @@
         <v>50</v>
       </c>
       <c r="E22" s="6">
-        <v>2379404.08</v>
+        <v>26636097.300000001</v>
       </c>
       <c r="F22" s="6">
-        <v>2225935.9700000002</v>
+        <v>23428345.600000001</v>
       </c>
       <c r="G22" s="6">
-        <v>2176937.8199999998</v>
+        <v>23202077.120000001</v>
       </c>
       <c r="H22" s="6">
-        <v>2225935.9700000002</v>
+        <v>23428345.600000001</v>
       </c>
       <c r="I22" s="7">
-        <v>177706.84</v>
+        <v>1862083.79</v>
       </c>
     </row>
     <row r="23" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -1509,7 +1497,7 @@
         <v>2026</v>
       </c>
       <c r="B23" s="4">
-        <v>2091</v>
+        <v>2271</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>51</v>
@@ -1518,19 +1506,19 @@
         <v>52</v>
       </c>
       <c r="E23" s="6">
-        <v>27950312.219999999</v>
+        <v>1072588308.5700001</v>
       </c>
       <c r="F23" s="6">
-        <v>27337708.899999999</v>
+        <v>971490602.75</v>
       </c>
       <c r="G23" s="6">
-        <v>26580425.079999998</v>
+        <v>926246955.15999997</v>
       </c>
       <c r="H23" s="6">
-        <v>27337708.899999999</v>
+        <v>971490602.75</v>
       </c>
       <c r="I23" s="7">
-        <v>1012564.28</v>
+        <v>94169427.730000004</v>
       </c>
     </row>
     <row r="24" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -1538,7 +1526,7 @@
         <v>2026</v>
       </c>
       <c r="B24" s="4">
-        <v>2261</v>
+        <v>2061</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>53</v>
@@ -1547,19 +1535,19 @@
         <v>54</v>
       </c>
       <c r="E24" s="6">
-        <v>215244365.56</v>
+        <v>29482811.149999999</v>
       </c>
       <c r="F24" s="6">
-        <v>125927156.79000001</v>
+        <v>27009835.739999998</v>
       </c>
       <c r="G24" s="6">
-        <v>117408851</v>
+        <v>26322141.890000001</v>
       </c>
       <c r="H24" s="6">
-        <v>125927156.79000001</v>
+        <v>27009835.739999998</v>
       </c>
       <c r="I24" s="7">
-        <v>140201064.78</v>
+        <v>1694176.47</v>
       </c>
     </row>
     <row r="25" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -1567,7 +1555,7 @@
         <v>2026</v>
       </c>
       <c r="B25" s="4">
-        <v>2151</v>
+        <v>2211</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>55</v>
@@ -1576,19 +1564,19 @@
         <v>56</v>
       </c>
       <c r="E25" s="6">
-        <v>26636097.300000001</v>
+        <v>6648668.1900000004</v>
       </c>
       <c r="F25" s="6">
-        <v>23378265.399999999</v>
+        <v>6043628.1100000003</v>
       </c>
       <c r="G25" s="6">
-        <v>23163900.010000002</v>
+        <v>5360722.3600000003</v>
       </c>
       <c r="H25" s="6">
-        <v>23378265.399999999</v>
+        <v>6043628.1100000003</v>
       </c>
       <c r="I25" s="7">
-        <v>1858623.42</v>
+        <v>560732.31000000006</v>
       </c>
     </row>
     <row r="26" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -1596,7 +1584,7 @@
         <v>2026</v>
       </c>
       <c r="B26" s="4">
-        <v>2271</v>
+        <v>4541</v>
       </c>
       <c r="C26" s="5" t="s">
         <v>57</v>
@@ -1605,19 +1593,19 @@
         <v>58</v>
       </c>
       <c r="E26" s="6">
-        <v>1062887229.61</v>
+        <v>238804</v>
       </c>
       <c r="F26" s="6">
-        <v>965585336.71000004</v>
+        <v>151205.25</v>
       </c>
       <c r="G26" s="6">
-        <v>923631541.95000005</v>
+        <v>142902.15</v>
       </c>
       <c r="H26" s="6">
-        <v>965585336.71000004</v>
+        <v>151205.25</v>
       </c>
       <c r="I26" s="7">
-        <v>94147754.609999999</v>
+        <v>28664.16</v>
       </c>
     </row>
     <row r="27" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -1625,7 +1613,7 @@
         <v>2026</v>
       </c>
       <c r="B27" s="4">
-        <v>2061</v>
+        <v>4551</v>
       </c>
       <c r="C27" s="5" t="s">
         <v>59</v>
@@ -1634,19 +1622,19 @@
         <v>60</v>
       </c>
       <c r="E27" s="6">
-        <v>29482441.23</v>
+        <v>63080228.539999999</v>
       </c>
       <c r="F27" s="6">
-        <v>26995697.219999999</v>
+        <v>53176826.32</v>
       </c>
       <c r="G27" s="6">
-        <v>26313658.390000001</v>
+        <v>53154020.079999998</v>
       </c>
       <c r="H27" s="6">
-        <v>26995697.219999999</v>
+        <v>53176826.32</v>
       </c>
       <c r="I27" s="7">
-        <v>1694176.47</v>
+        <v>486647</v>
       </c>
     </row>
     <row r="28" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -1654,7 +1642,7 @@
         <v>2026</v>
       </c>
       <c r="B28" s="4">
-        <v>2211</v>
+        <v>4331</v>
       </c>
       <c r="C28" s="5" t="s">
         <v>61</v>
@@ -1663,19 +1651,19 @@
         <v>62</v>
       </c>
       <c r="E28" s="6">
-        <v>6619334.1900000004</v>
+        <v>2643527.87</v>
       </c>
       <c r="F28" s="6">
-        <v>6043628.1100000003</v>
+        <v>0</v>
       </c>
       <c r="G28" s="6">
-        <v>5360722.3600000003</v>
+        <v>0</v>
       </c>
       <c r="H28" s="6">
-        <v>6043628.1100000003</v>
+        <v>0</v>
       </c>
       <c r="I28" s="7">
-        <v>560732.31000000006</v>
+        <v>249016.26</v>
       </c>
     </row>
     <row r="29" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -1683,7 +1671,7 @@
         <v>2026</v>
       </c>
       <c r="B29" s="4">
-        <v>4541</v>
+        <v>4631</v>
       </c>
       <c r="C29" s="5" t="s">
         <v>63</v>
@@ -1692,19 +1680,19 @@
         <v>64</v>
       </c>
       <c r="E29" s="6">
-        <v>238804</v>
+        <v>420239681.18000001</v>
       </c>
       <c r="F29" s="6">
-        <v>132007.37</v>
+        <v>133548550.97</v>
       </c>
       <c r="G29" s="6">
-        <v>125364.89</v>
+        <v>122228011.7</v>
       </c>
       <c r="H29" s="6">
-        <v>132007.37</v>
+        <v>133548550.97</v>
       </c>
       <c r="I29" s="7">
-        <v>28664.16</v>
+        <v>89063165.060000002</v>
       </c>
     </row>
     <row r="30" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -1712,7 +1700,7 @@
         <v>2026</v>
       </c>
       <c r="B30" s="4">
-        <v>4551</v>
+        <v>4341</v>
       </c>
       <c r="C30" s="5" t="s">
         <v>65</v>
@@ -1721,19 +1709,19 @@
         <v>66</v>
       </c>
       <c r="E30" s="6">
-        <v>63080228.539999999</v>
+        <v>301819.55</v>
       </c>
       <c r="F30" s="6">
-        <v>53176826.32</v>
+        <v>253902.69</v>
       </c>
       <c r="G30" s="6">
-        <v>53154020.079999998</v>
+        <v>237233.7</v>
       </c>
       <c r="H30" s="6">
-        <v>53176826.32</v>
+        <v>253902.69</v>
       </c>
       <c r="I30" s="7">
-        <v>486647</v>
+        <v>353339.8</v>
       </c>
     </row>
     <row r="31" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -1741,7 +1729,7 @@
         <v>2026</v>
       </c>
       <c r="B31" s="4">
-        <v>4331</v>
+        <v>4751</v>
       </c>
       <c r="C31" s="5" t="s">
         <v>67</v>
@@ -1750,27 +1738,25 @@
         <v>68</v>
       </c>
       <c r="E31" s="6">
-        <v>2643527.87</v>
+        <v>5131363.57</v>
       </c>
       <c r="F31" s="6">
-        <v>0</v>
+        <v>2072533.6</v>
       </c>
       <c r="G31" s="6">
-        <v>0</v>
+        <v>869473.52</v>
       </c>
       <c r="H31" s="6">
-        <v>0</v>
-      </c>
-      <c r="I31" s="7">
-        <v>249016.26</v>
-      </c>
+        <v>2072533.6</v>
+      </c>
+      <c r="I31" s="7"/>
     </row>
     <row r="32" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="4">
         <v>2026</v>
       </c>
       <c r="B32" s="4">
-        <v>4631</v>
+        <v>4251</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>69</v>
@@ -1779,19 +1765,19 @@
         <v>70</v>
       </c>
       <c r="E32" s="6">
-        <v>420239681.18000001</v>
+        <v>70218221.569999993</v>
       </c>
       <c r="F32" s="6">
-        <v>133548550.97</v>
+        <v>50973254.369999997</v>
       </c>
       <c r="G32" s="6">
-        <v>122228011.7</v>
+        <v>45737504.140000001</v>
       </c>
       <c r="H32" s="6">
-        <v>133548550.97</v>
+        <v>50973254.369999997</v>
       </c>
       <c r="I32" s="7">
-        <v>89063165.060000002</v>
+        <v>1466576.12</v>
       </c>
     </row>
     <row r="33" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -1799,7 +1785,7 @@
         <v>2026</v>
       </c>
       <c r="B33" s="4">
-        <v>4341</v>
+        <v>4491</v>
       </c>
       <c r="C33" s="5" t="s">
         <v>71</v>
@@ -1808,19 +1794,19 @@
         <v>72</v>
       </c>
       <c r="E33" s="6">
-        <v>265198.11</v>
+        <v>11214.34</v>
       </c>
       <c r="F33" s="6">
-        <v>253902.69</v>
+        <v>11214.34</v>
       </c>
       <c r="G33" s="6">
-        <v>237233.7</v>
+        <v>11214.34</v>
       </c>
       <c r="H33" s="6">
-        <v>253902.69</v>
+        <v>11214.34</v>
       </c>
       <c r="I33" s="7">
-        <v>353339.8</v>
+        <v>134615.38</v>
       </c>
     </row>
     <row r="34" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -1828,7 +1814,7 @@
         <v>2026</v>
       </c>
       <c r="B34" s="4">
-        <v>4751</v>
+        <v>4381</v>
       </c>
       <c r="C34" s="5" t="s">
         <v>73</v>
@@ -1837,25 +1823,27 @@
         <v>74</v>
       </c>
       <c r="E34" s="6">
-        <v>5118463.57</v>
+        <v>64033251.479999997</v>
       </c>
       <c r="F34" s="6">
-        <v>2071889.3</v>
+        <v>25710237.670000002</v>
       </c>
       <c r="G34" s="6">
-        <v>868829.22</v>
+        <v>23494181.870000001</v>
       </c>
       <c r="H34" s="6">
-        <v>2071889.3</v>
-      </c>
-      <c r="I34" s="7"/>
+        <v>25710237.670000002</v>
+      </c>
+      <c r="I34" s="7">
+        <v>17655143.399999999</v>
+      </c>
     </row>
     <row r="35" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
         <v>2026</v>
       </c>
       <c r="B35" s="4">
-        <v>4251</v>
+        <v>4101</v>
       </c>
       <c r="C35" s="5" t="s">
         <v>75</v>
@@ -1864,19 +1852,19 @@
         <v>76</v>
       </c>
       <c r="E35" s="6">
-        <v>70175650.920000002</v>
+        <v>5271038.8099999996</v>
       </c>
       <c r="F35" s="6">
-        <v>50484148</v>
+        <v>5271038.8099999996</v>
       </c>
       <c r="G35" s="6">
-        <v>45690974.25</v>
+        <v>5271038.8099999996</v>
       </c>
       <c r="H35" s="6">
-        <v>50484148</v>
+        <v>5271038.8099999996</v>
       </c>
       <c r="I35" s="7">
-        <v>1466576.12</v>
+        <v>360498.89</v>
       </c>
     </row>
     <row r="36" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -1884,7 +1872,7 @@
         <v>2026</v>
       </c>
       <c r="B36" s="4">
-        <v>4491</v>
+        <v>4291</v>
       </c>
       <c r="C36" s="5" t="s">
         <v>77</v>
@@ -1893,19 +1881,19 @@
         <v>78</v>
       </c>
       <c r="E36" s="6">
-        <v>11214.34</v>
+        <v>7821400828.04</v>
       </c>
       <c r="F36" s="6">
-        <v>11214.34</v>
+        <v>5230382858.21</v>
       </c>
       <c r="G36" s="6">
-        <v>11214.34</v>
+        <v>4352421107.7799997</v>
       </c>
       <c r="H36" s="6">
-        <v>11214.34</v>
+        <v>5230382858.21</v>
       </c>
       <c r="I36" s="7">
-        <v>134615.38</v>
+        <v>748713704.79999995</v>
       </c>
     </row>
     <row r="37" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -1913,7 +1901,7 @@
         <v>2026</v>
       </c>
       <c r="B37" s="4">
-        <v>4381</v>
+        <v>4691</v>
       </c>
       <c r="C37" s="5" t="s">
         <v>79</v>
@@ -1922,19 +1910,19 @@
         <v>80</v>
       </c>
       <c r="E37" s="6">
-        <v>64033251.479999997</v>
+        <v>16916519.640000001</v>
       </c>
       <c r="F37" s="6">
-        <v>25127703.77</v>
+        <v>4143592</v>
       </c>
       <c r="G37" s="6">
-        <v>23486106.84</v>
+        <v>2822568.13</v>
       </c>
       <c r="H37" s="6">
-        <v>25127703.77</v>
+        <v>4143592</v>
       </c>
       <c r="I37" s="7">
-        <v>17655143.399999999</v>
+        <v>33321209.530000001</v>
       </c>
     </row>
     <row r="38" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -1942,7 +1930,7 @@
         <v>2026</v>
       </c>
       <c r="B38" s="4">
-        <v>4101</v>
+        <v>4701</v>
       </c>
       <c r="C38" s="5" t="s">
         <v>81</v>
@@ -1951,19 +1939,19 @@
         <v>82</v>
       </c>
       <c r="E38" s="6">
-        <v>5271038.8099999996</v>
+        <v>347313.03</v>
       </c>
       <c r="F38" s="6">
-        <v>5271038.8099999996</v>
+        <v>100554.43</v>
       </c>
       <c r="G38" s="6">
-        <v>5271038.8099999996</v>
+        <v>98828.63</v>
       </c>
       <c r="H38" s="6">
-        <v>5271038.8099999996</v>
+        <v>100554.43</v>
       </c>
       <c r="I38" s="7">
-        <v>360498.89</v>
+        <v>1235436.6200000001</v>
       </c>
     </row>
     <row r="39" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -1971,7 +1959,7 @@
         <v>2026</v>
       </c>
       <c r="B39" s="4">
-        <v>4291</v>
+        <v>4711</v>
       </c>
       <c r="C39" s="5" t="s">
         <v>83</v>
@@ -1980,19 +1968,19 @@
         <v>84</v>
       </c>
       <c r="E39" s="6">
-        <v>7820622014.9099998</v>
+        <v>7338220523.8400002</v>
       </c>
       <c r="F39" s="6">
-        <v>5115241375.8400002</v>
+        <v>7334093481.1000004</v>
       </c>
       <c r="G39" s="6">
-        <v>4238918482.04</v>
+        <v>7333974808.0600004</v>
       </c>
       <c r="H39" s="6">
-        <v>5115241375.8400002</v>
+        <v>7334093481.1000004</v>
       </c>
       <c r="I39" s="7">
-        <v>748625337.77999997</v>
+        <v>817342.46</v>
       </c>
     </row>
     <row r="40" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -2000,7 +1988,7 @@
         <v>2026</v>
       </c>
       <c r="B40" s="4">
-        <v>4691</v>
+        <v>4141</v>
       </c>
       <c r="C40" s="5" t="s">
         <v>85</v>
@@ -2009,19 +1997,19 @@
         <v>86</v>
       </c>
       <c r="E40" s="6">
-        <v>16253745.640000001</v>
+        <v>123226.75</v>
       </c>
       <c r="F40" s="6">
-        <v>3873125.58</v>
+        <v>0</v>
       </c>
       <c r="G40" s="6">
-        <v>2694827.53</v>
+        <v>0</v>
       </c>
       <c r="H40" s="6">
-        <v>3873125.58</v>
+        <v>0</v>
       </c>
       <c r="I40" s="7">
-        <v>33321209.530000001</v>
+        <v>155231.67999999999</v>
       </c>
     </row>
     <row r="41" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -2029,7 +2017,7 @@
         <v>2026</v>
       </c>
       <c r="B41" s="4">
-        <v>4701</v>
+        <v>1071</v>
       </c>
       <c r="C41" s="5" t="s">
         <v>87</v>
@@ -2038,19 +2026,19 @@
         <v>88</v>
       </c>
       <c r="E41" s="6">
-        <v>347313.03</v>
+        <v>51141442.75</v>
       </c>
       <c r="F41" s="6">
-        <v>98335.53</v>
+        <v>22809169.390000001</v>
       </c>
       <c r="G41" s="6">
-        <v>96609.73</v>
+        <v>20044207.539999999</v>
       </c>
       <c r="H41" s="6">
-        <v>98335.53</v>
+        <v>22809169.390000001</v>
       </c>
       <c r="I41" s="7">
-        <v>1235436.6200000001</v>
+        <v>12951127.779999999</v>
       </c>
     </row>
     <row r="42" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -2058,7 +2046,7 @@
         <v>2026</v>
       </c>
       <c r="B42" s="4">
-        <v>4711</v>
+        <v>1916</v>
       </c>
       <c r="C42" s="5" t="s">
         <v>89</v>
@@ -2067,19 +2055,19 @@
         <v>90</v>
       </c>
       <c r="E42" s="6">
-        <v>7338197840.8900003</v>
+        <v>3583448472.29</v>
       </c>
       <c r="F42" s="6">
-        <v>7334070798.1499996</v>
+        <v>2645309163.7600002</v>
       </c>
       <c r="G42" s="6">
-        <v>7333952141.75</v>
+        <v>2603731154.6500001</v>
       </c>
       <c r="H42" s="6">
-        <v>7334070798.1499996</v>
+        <v>2645309163.7600002</v>
       </c>
       <c r="I42" s="7">
-        <v>817342.46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -2087,7 +2075,7 @@
         <v>2026</v>
       </c>
       <c r="B43" s="4">
-        <v>4141</v>
+        <v>2421</v>
       </c>
       <c r="C43" s="5" t="s">
         <v>91</v>
@@ -2096,19 +2084,19 @@
         <v>92</v>
       </c>
       <c r="E43" s="6">
-        <v>123226.75</v>
+        <v>21461022.969999999</v>
       </c>
       <c r="F43" s="6">
-        <v>0</v>
+        <v>11838484.560000001</v>
       </c>
       <c r="G43" s="6">
-        <v>0</v>
+        <v>11527040.24</v>
       </c>
       <c r="H43" s="6">
-        <v>0</v>
+        <v>11838484.560000001</v>
       </c>
       <c r="I43" s="7">
-        <v>155231.67999999999</v>
+        <v>19204544.77</v>
       </c>
     </row>
     <row r="44" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -2116,7 +2104,7 @@
         <v>2026</v>
       </c>
       <c r="B44" s="4">
-        <v>1071</v>
+        <v>2331</v>
       </c>
       <c r="C44" s="5" t="s">
         <v>93</v>
@@ -2125,19 +2113,19 @@
         <v>94</v>
       </c>
       <c r="E44" s="6">
-        <v>51037875.149999999</v>
+        <v>15114419.550000001</v>
       </c>
       <c r="F44" s="6">
-        <v>22772747.289999999</v>
+        <v>14407056.550000001</v>
       </c>
       <c r="G44" s="6">
-        <v>19921402.449999999</v>
+        <v>13868182.199999999</v>
       </c>
       <c r="H44" s="6">
-        <v>22772747.289999999</v>
+        <v>14407056.550000001</v>
       </c>
       <c r="I44" s="7">
-        <v>12951127.779999999</v>
+        <v>1193954.9099999999</v>
       </c>
     </row>
     <row r="45" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -2145,7 +2133,7 @@
         <v>2026</v>
       </c>
       <c r="B45" s="4">
-        <v>1916</v>
+        <v>2011</v>
       </c>
       <c r="C45" s="5" t="s">
         <v>95</v>
@@ -2154,19 +2142,19 @@
         <v>96</v>
       </c>
       <c r="E45" s="6">
-        <v>3583448472.29</v>
+        <v>1014506387.9</v>
       </c>
       <c r="F45" s="6">
-        <v>2645309163.7600002</v>
+        <v>636217771.83000004</v>
       </c>
       <c r="G45" s="6">
-        <v>2603731154.6500001</v>
+        <v>620212889.98000002</v>
       </c>
       <c r="H45" s="6">
-        <v>2645309163.7600002</v>
+        <v>636217771.83000004</v>
       </c>
       <c r="I45" s="7">
-        <v>0</v>
+        <v>188967563.97999999</v>
       </c>
     </row>
     <row r="46" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -2174,7 +2162,7 @@
         <v>2026</v>
       </c>
       <c r="B46" s="4">
-        <v>2421</v>
+        <v>2121</v>
       </c>
       <c r="C46" s="5" t="s">
         <v>97</v>
@@ -2183,19 +2171,19 @@
         <v>98</v>
       </c>
       <c r="E46" s="6">
-        <v>21296022.989999998</v>
+        <v>1327074862.6199999</v>
       </c>
       <c r="F46" s="6">
-        <v>11768679.99</v>
+        <v>1307006346.6500001</v>
       </c>
       <c r="G46" s="6">
-        <v>11444414.49</v>
+        <v>1291429263.22</v>
       </c>
       <c r="H46" s="6">
-        <v>11768679.99</v>
+        <v>1307006346.6500001</v>
       </c>
       <c r="I46" s="7">
-        <v>19032827.77</v>
+        <v>53697699.990000002</v>
       </c>
     </row>
     <row r="47" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -2203,7 +2191,7 @@
         <v>2026</v>
       </c>
       <c r="B47" s="4">
-        <v>2331</v>
+        <v>2101</v>
       </c>
       <c r="C47" s="5" t="s">
         <v>99</v>
@@ -2212,19 +2200,19 @@
         <v>100</v>
       </c>
       <c r="E47" s="6">
-        <v>15109050.68</v>
+        <v>95159257.299999997</v>
       </c>
       <c r="F47" s="6">
-        <v>14385151.109999999</v>
+        <v>84582248.359999999</v>
       </c>
       <c r="G47" s="6">
-        <v>13847217.33</v>
+        <v>80399748.400000006</v>
       </c>
       <c r="H47" s="6">
-        <v>14385151.109999999</v>
+        <v>84582248.359999999</v>
       </c>
       <c r="I47" s="7">
-        <v>1193954.9099999999</v>
+        <v>7228899.0499999998</v>
       </c>
     </row>
     <row r="48" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -2232,7 +2220,7 @@
         <v>2026</v>
       </c>
       <c r="B48" s="4">
-        <v>2011</v>
+        <v>2201</v>
       </c>
       <c r="C48" s="5" t="s">
         <v>101</v>
@@ -2241,19 +2229,19 @@
         <v>102</v>
       </c>
       <c r="E48" s="6">
-        <v>1012498696.89</v>
+        <v>10910190.560000001</v>
       </c>
       <c r="F48" s="6">
-        <v>628352812.44000006</v>
+        <v>7514308.6900000004</v>
       </c>
       <c r="G48" s="6">
-        <v>610327717.67999995</v>
+        <v>6983344.9500000002</v>
       </c>
       <c r="H48" s="6">
-        <v>628352812.44000006</v>
+        <v>7514308.6900000004</v>
       </c>
       <c r="I48" s="7">
-        <v>188965891.83000001</v>
+        <v>1123384.71</v>
       </c>
     </row>
     <row r="49" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -2261,7 +2249,7 @@
         <v>2026</v>
       </c>
       <c r="B49" s="4">
-        <v>2121</v>
+        <v>2371</v>
       </c>
       <c r="C49" s="5" t="s">
         <v>103</v>
@@ -2270,19 +2258,19 @@
         <v>104</v>
       </c>
       <c r="E49" s="6">
-        <v>1325177225.8900001</v>
+        <v>126877262.7</v>
       </c>
       <c r="F49" s="6">
-        <v>1305325028.45</v>
+        <v>121102979.84</v>
       </c>
       <c r="G49" s="6">
-        <v>1289855661.6199999</v>
+        <v>120208444.76000001</v>
       </c>
       <c r="H49" s="6">
-        <v>1305325028.45</v>
+        <v>121102979.84</v>
       </c>
       <c r="I49" s="7">
-        <v>53697699.990000002</v>
+        <v>4994759.12</v>
       </c>
     </row>
     <row r="50" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -2290,7 +2278,7 @@
         <v>2026</v>
       </c>
       <c r="B50" s="4">
-        <v>2101</v>
+        <v>2241</v>
       </c>
       <c r="C50" s="5" t="s">
         <v>105</v>
@@ -2299,19 +2287,19 @@
         <v>106</v>
       </c>
       <c r="E50" s="6">
-        <v>94435034.909999996</v>
+        <v>23260929.870000001</v>
       </c>
       <c r="F50" s="6">
-        <v>83722222.159999996</v>
+        <v>19958139.5</v>
       </c>
       <c r="G50" s="6">
-        <v>80053983</v>
+        <v>18477522.579999998</v>
       </c>
       <c r="H50" s="6">
-        <v>83722222.159999996</v>
+        <v>19958139.5</v>
       </c>
       <c r="I50" s="7">
-        <v>7228899.0499999998</v>
+        <v>15335922.720000001</v>
       </c>
     </row>
     <row r="51" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -2319,7 +2307,7 @@
         <v>2026</v>
       </c>
       <c r="B51" s="4">
-        <v>2201</v>
+        <v>2251</v>
       </c>
       <c r="C51" s="5" t="s">
         <v>107</v>
@@ -2328,19 +2316,19 @@
         <v>108</v>
       </c>
       <c r="E51" s="6">
-        <v>10824762.630000001</v>
+        <v>18211576.539999999</v>
       </c>
       <c r="F51" s="6">
-        <v>7489444.2599999998</v>
+        <v>15586413.68</v>
       </c>
       <c r="G51" s="6">
-        <v>6958480.5199999996</v>
+        <v>14588127.529999999</v>
       </c>
       <c r="H51" s="6">
-        <v>7489444.2599999998</v>
+        <v>15586413.68</v>
       </c>
       <c r="I51" s="7">
-        <v>1123384.71</v>
+        <v>2979183.08</v>
       </c>
     </row>
     <row r="52" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -2348,7 +2336,7 @@
         <v>2026</v>
       </c>
       <c r="B52" s="4">
-        <v>2371</v>
+        <v>2041</v>
       </c>
       <c r="C52" s="5" t="s">
         <v>109</v>
@@ -2357,19 +2345,19 @@
         <v>110</v>
       </c>
       <c r="E52" s="6">
-        <v>126744560.45</v>
+        <v>1421219.12</v>
       </c>
       <c r="F52" s="6">
-        <v>121042703.14</v>
+        <v>1314597.3400000001</v>
       </c>
       <c r="G52" s="6">
-        <v>120103616.70999999</v>
+        <v>1289253.21</v>
       </c>
       <c r="H52" s="6">
-        <v>121042703.14</v>
+        <v>1314597.3400000001</v>
       </c>
       <c r="I52" s="7">
-        <v>4994759.12</v>
+        <v>34003.33</v>
       </c>
     </row>
     <row r="53" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -2377,7 +2365,7 @@
         <v>2026</v>
       </c>
       <c r="B53" s="4">
-        <v>2241</v>
+        <v>1101</v>
       </c>
       <c r="C53" s="5" t="s">
         <v>111</v>
@@ -2386,19 +2374,19 @@
         <v>112</v>
       </c>
       <c r="E53" s="6">
-        <v>23158195.59</v>
+        <v>8420821.4600000009</v>
       </c>
       <c r="F53" s="6">
-        <v>19862176.530000001</v>
+        <v>7806907.4699999997</v>
       </c>
       <c r="G53" s="6">
-        <v>18462833.420000002</v>
+        <v>7759680.4000000004</v>
       </c>
       <c r="H53" s="6">
-        <v>19862176.530000001</v>
+        <v>7806907.4699999997</v>
       </c>
       <c r="I53" s="7">
-        <v>15335922.720000001</v>
+        <v>93457.72</v>
       </c>
     </row>
     <row r="54" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -2406,7 +2394,7 @@
         <v>2026</v>
       </c>
       <c r="B54" s="4">
-        <v>2251</v>
+        <v>1915</v>
       </c>
       <c r="C54" s="5" t="s">
         <v>113</v>
@@ -2415,27 +2403,25 @@
         <v>114</v>
       </c>
       <c r="E54" s="6">
-        <v>18576838.039999999</v>
+        <v>12949020.939999999</v>
       </c>
       <c r="F54" s="6">
-        <v>15586163.98</v>
+        <v>10390853.25</v>
       </c>
       <c r="G54" s="6">
-        <v>14588127.529999999</v>
+        <v>10390853.25</v>
       </c>
       <c r="H54" s="6">
-        <v>15586163.98</v>
-      </c>
-      <c r="I54" s="7">
-        <v>2979183.08</v>
-      </c>
+        <v>10390853.25</v>
+      </c>
+      <c r="I54" s="7"/>
     </row>
     <row r="55" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="4">
         <v>2026</v>
       </c>
       <c r="B55" s="4">
-        <v>2041</v>
+        <v>1511</v>
       </c>
       <c r="C55" s="5" t="s">
         <v>115</v>
@@ -2444,19 +2430,19 @@
         <v>116</v>
       </c>
       <c r="E55" s="6">
-        <v>1421219.12</v>
+        <v>1351149804.6800001</v>
       </c>
       <c r="F55" s="6">
-        <v>1314597.3400000001</v>
+        <v>1296028565.29</v>
       </c>
       <c r="G55" s="6">
-        <v>1289253.21</v>
+        <v>1271686429.8099999</v>
       </c>
       <c r="H55" s="6">
-        <v>1314597.3400000001</v>
+        <v>1296028565.29</v>
       </c>
       <c r="I55" s="7">
-        <v>34003.33</v>
+        <v>37140299.280000001</v>
       </c>
     </row>
     <row r="56" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -2464,7 +2450,7 @@
         <v>2026</v>
       </c>
       <c r="B56" s="4">
-        <v>1101</v>
+        <v>1251</v>
       </c>
       <c r="C56" s="5" t="s">
         <v>117</v>
@@ -2473,19 +2459,19 @@
         <v>118</v>
       </c>
       <c r="E56" s="6">
-        <v>8420821.4600000009</v>
+        <v>7273085470.0100002</v>
       </c>
       <c r="F56" s="6">
-        <v>7806907.4699999997</v>
+        <v>7093098688.1000004</v>
       </c>
       <c r="G56" s="6">
-        <v>7759680.4000000004</v>
+        <v>7069817769.9399996</v>
       </c>
       <c r="H56" s="6">
-        <v>7806907.4699999997</v>
+        <v>7093098688.1000004</v>
       </c>
       <c r="I56" s="7">
-        <v>93457.72</v>
+        <v>154346621.11000001</v>
       </c>
     </row>
     <row r="57" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -2493,7 +2479,7 @@
         <v>2026</v>
       </c>
       <c r="B57" s="4">
-        <v>1915</v>
+        <v>1721</v>
       </c>
       <c r="C57" s="5" t="s">
         <v>119</v>
@@ -2502,25 +2488,27 @@
         <v>120</v>
       </c>
       <c r="E57" s="6">
-        <v>12949020.939999999</v>
+        <v>4112200.56</v>
       </c>
       <c r="F57" s="6">
-        <v>10390853.25</v>
+        <v>4054091.4</v>
       </c>
       <c r="G57" s="6">
-        <v>10390853.25</v>
+        <v>3919051.73</v>
       </c>
       <c r="H57" s="6">
-        <v>10390853.25</v>
-      </c>
-      <c r="I57" s="7"/>
+        <v>4054091.4</v>
+      </c>
+      <c r="I57" s="7">
+        <v>336771.97</v>
+      </c>
     </row>
     <row r="58" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="4">
         <v>2026</v>
       </c>
       <c r="B58" s="4">
-        <v>1511</v>
+        <v>1231</v>
       </c>
       <c r="C58" s="5" t="s">
         <v>121</v>
@@ -2529,19 +2517,19 @@
         <v>122</v>
       </c>
       <c r="E58" s="6">
-        <v>1350173518.46</v>
+        <v>129482222.59999999</v>
       </c>
       <c r="F58" s="6">
-        <v>1294556909.0799999</v>
+        <v>66306884.210000001</v>
       </c>
       <c r="G58" s="6">
-        <v>1271572014.4400001</v>
+        <v>65599551.530000001</v>
       </c>
       <c r="H58" s="6">
-        <v>1294556909.0799999</v>
+        <v>66306884.210000001</v>
       </c>
       <c r="I58" s="7">
-        <v>37137899.359999999</v>
+        <v>21754072.289999999</v>
       </c>
     </row>
     <row r="59" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -2549,7 +2537,7 @@
         <v>2026</v>
       </c>
       <c r="B59" s="4">
-        <v>1251</v>
+        <v>1711</v>
       </c>
       <c r="C59" s="5" t="s">
         <v>123</v>
@@ -2558,19 +2546,19 @@
         <v>124</v>
       </c>
       <c r="E59" s="6">
-        <v>7269176777.2299995</v>
+        <v>80244337.189999998</v>
       </c>
       <c r="F59" s="6">
-        <v>7090188531.2299995</v>
+        <v>23905382.34</v>
       </c>
       <c r="G59" s="6">
-        <v>7069525654.9200001</v>
+        <v>21868504.949999999</v>
       </c>
       <c r="H59" s="6">
-        <v>7090188531.2299995</v>
+        <v>23905382.34</v>
       </c>
       <c r="I59" s="7">
-        <v>154331376.27000001</v>
+        <v>50078579.609999999</v>
       </c>
     </row>
     <row r="60" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -2578,7 +2566,7 @@
         <v>2026</v>
       </c>
       <c r="B60" s="4">
-        <v>1721</v>
+        <v>1271</v>
       </c>
       <c r="C60" s="5" t="s">
         <v>125</v>
@@ -2587,19 +2575,19 @@
         <v>126</v>
       </c>
       <c r="E60" s="6">
-        <v>4112200.56</v>
+        <v>39868099.350000001</v>
       </c>
       <c r="F60" s="6">
-        <v>4011744.89</v>
+        <v>31664500.760000002</v>
       </c>
       <c r="G60" s="6">
-        <v>3919051.73</v>
+        <v>30353244.210000001</v>
       </c>
       <c r="H60" s="6">
-        <v>4011744.89</v>
+        <v>31664500.760000002</v>
       </c>
       <c r="I60" s="7">
-        <v>336771.97</v>
+        <v>939890.1</v>
       </c>
     </row>
     <row r="61" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -2607,7 +2595,7 @@
         <v>2026</v>
       </c>
       <c r="B61" s="4">
-        <v>1231</v>
+        <v>1221</v>
       </c>
       <c r="C61" s="5" t="s">
         <v>127</v>
@@ -2616,19 +2604,19 @@
         <v>128</v>
       </c>
       <c r="E61" s="6">
-        <v>128924936.2</v>
+        <v>41524320.07</v>
       </c>
       <c r="F61" s="6">
-        <v>66292983.659999996</v>
+        <v>20940647.120000001</v>
       </c>
       <c r="G61" s="6">
-        <v>65589487.380000003</v>
+        <v>20245429.850000001</v>
       </c>
       <c r="H61" s="6">
-        <v>66292983.659999996</v>
+        <v>20940647.120000001</v>
       </c>
       <c r="I61" s="7">
-        <v>21754072.289999999</v>
+        <v>23205532.539999999</v>
       </c>
     </row>
     <row r="62" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -2636,7 +2624,7 @@
         <v>2026</v>
       </c>
       <c r="B62" s="4">
-        <v>1711</v>
+        <v>1481</v>
       </c>
       <c r="C62" s="5" t="s">
         <v>129</v>
@@ -2645,19 +2633,19 @@
         <v>130</v>
       </c>
       <c r="E62" s="6">
-        <v>77144389.349999994</v>
+        <v>57033203.259999998</v>
       </c>
       <c r="F62" s="6">
-        <v>23392383.219999999</v>
+        <v>53832098.859999999</v>
       </c>
       <c r="G62" s="6">
-        <v>21868772.23</v>
+        <v>49143815.75</v>
       </c>
       <c r="H62" s="6">
-        <v>23392383.219999999</v>
+        <v>53832098.859999999</v>
       </c>
       <c r="I62" s="7">
-        <v>50078579.609999999</v>
+        <v>24862865.079999998</v>
       </c>
     </row>
     <row r="63" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -2665,7 +2653,7 @@
         <v>2026</v>
       </c>
       <c r="B63" s="4">
-        <v>1271</v>
+        <v>1261</v>
       </c>
       <c r="C63" s="5" t="s">
         <v>131</v>
@@ -2674,19 +2662,19 @@
         <v>132</v>
       </c>
       <c r="E63" s="6">
-        <v>39867399.840000004</v>
+        <v>8052235836.0799999</v>
       </c>
       <c r="F63" s="6">
-        <v>31632063.16</v>
+        <v>7752182447.1000004</v>
       </c>
       <c r="G63" s="6">
-        <v>30353052.329999998</v>
+        <v>7611083364.6899996</v>
       </c>
       <c r="H63" s="6">
-        <v>31632063.16</v>
+        <v>7752182447.1000004</v>
       </c>
       <c r="I63" s="7">
-        <v>939890.1</v>
+        <v>317068028.00999999</v>
       </c>
     </row>
     <row r="64" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -2694,7 +2682,7 @@
         <v>2026</v>
       </c>
       <c r="B64" s="4">
-        <v>1221</v>
+        <v>1191</v>
       </c>
       <c r="C64" s="5" t="s">
         <v>133</v>
@@ -2703,19 +2691,19 @@
         <v>134</v>
       </c>
       <c r="E64" s="6">
-        <v>41520431.770000003</v>
+        <v>783489981.63</v>
       </c>
       <c r="F64" s="6">
-        <v>20865898.309999999</v>
+        <v>710069001.65999997</v>
       </c>
       <c r="G64" s="6">
-        <v>20179264.710000001</v>
+        <v>691109821.25999999</v>
       </c>
       <c r="H64" s="6">
-        <v>20865898.309999999</v>
+        <v>710069001.65999997</v>
       </c>
       <c r="I64" s="7">
-        <v>22734064.84</v>
+        <v>61324169.560000002</v>
       </c>
     </row>
     <row r="65" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -2723,7 +2711,7 @@
         <v>2026</v>
       </c>
       <c r="B65" s="4">
-        <v>1481</v>
+        <v>1491</v>
       </c>
       <c r="C65" s="5" t="s">
         <v>135</v>
@@ -2732,19 +2720,19 @@
         <v>136</v>
       </c>
       <c r="E65" s="6">
-        <v>56004716.119999997</v>
+        <v>182627485.16999999</v>
       </c>
       <c r="F65" s="6">
-        <v>53209569.399999999</v>
+        <v>171077586.84999999</v>
       </c>
       <c r="G65" s="6">
-        <v>49113343.719999999</v>
+        <v>47034426.729999997</v>
       </c>
       <c r="H65" s="6">
-        <v>53209569.399999999</v>
+        <v>171077586.84999999</v>
       </c>
       <c r="I65" s="7">
-        <v>24723701.969999999</v>
+        <v>15500389.380000001</v>
       </c>
     </row>
     <row r="66" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -2752,7 +2740,7 @@
         <v>2026</v>
       </c>
       <c r="B66" s="4">
-        <v>1261</v>
+        <v>1301</v>
       </c>
       <c r="C66" s="5" t="s">
         <v>137</v>
@@ -2761,19 +2749,19 @@
         <v>138</v>
       </c>
       <c r="E66" s="6">
-        <v>8024349050.9200001</v>
+        <v>356778047.43000001</v>
       </c>
       <c r="F66" s="6">
-        <v>7747706024.3199997</v>
+        <v>341232051.48000002</v>
       </c>
       <c r="G66" s="6">
-        <v>7594526671.3299999</v>
+        <v>59912472.469999999</v>
       </c>
       <c r="H66" s="6">
-        <v>7747706024.3199997</v>
+        <v>341232051.48000002</v>
       </c>
       <c r="I66" s="7">
-        <v>317043917.64999998</v>
+        <v>39067518.859999999</v>
       </c>
     </row>
     <row r="67" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -2781,7 +2769,7 @@
         <v>2026</v>
       </c>
       <c r="B67" s="4">
-        <v>1191</v>
+        <v>1451</v>
       </c>
       <c r="C67" s="5" t="s">
         <v>139</v>
@@ -2790,19 +2778,19 @@
         <v>140</v>
       </c>
       <c r="E67" s="6">
-        <v>782476481.16999996</v>
+        <v>2095137569.5799999</v>
       </c>
       <c r="F67" s="6">
-        <v>708196151.51999998</v>
+        <v>1787370024.45</v>
       </c>
       <c r="G67" s="6">
-        <v>690159679.27999997</v>
+        <v>1741292355.3599999</v>
       </c>
       <c r="H67" s="6">
-        <v>708196151.51999998</v>
+        <v>1787370024.45</v>
       </c>
       <c r="I67" s="7">
-        <v>60370616.219999999</v>
+        <v>132761469.72</v>
       </c>
     </row>
     <row r="68" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -2810,7 +2798,7 @@
         <v>2026</v>
       </c>
       <c r="B68" s="4">
-        <v>1491</v>
+        <v>1371</v>
       </c>
       <c r="C68" s="5" t="s">
         <v>141</v>
@@ -2819,19 +2807,19 @@
         <v>142</v>
       </c>
       <c r="E68" s="6">
-        <v>158953134.34999999</v>
+        <v>94238901.75</v>
       </c>
       <c r="F68" s="6">
-        <v>130625007.09999999</v>
+        <v>87131954.370000005</v>
       </c>
       <c r="G68" s="6">
-        <v>47031008.530000001</v>
+        <v>85297204.519999996</v>
       </c>
       <c r="H68" s="6">
-        <v>130625007.09999999</v>
+        <v>87131954.370000005</v>
       </c>
       <c r="I68" s="7">
-        <v>15500389.380000001</v>
+        <v>8157878.4699999997</v>
       </c>
     </row>
     <row r="69" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -2839,7 +2827,7 @@
         <v>2026</v>
       </c>
       <c r="B69" s="4">
-        <v>1301</v>
+        <v>1501</v>
       </c>
       <c r="C69" s="5" t="s">
         <v>143</v>
@@ -2848,19 +2836,19 @@
         <v>144</v>
       </c>
       <c r="E69" s="6">
-        <v>349334531.31</v>
+        <v>331698744.00999999</v>
       </c>
       <c r="F69" s="6">
-        <v>290136718.94</v>
+        <v>255209641.13999999</v>
       </c>
       <c r="G69" s="6">
-        <v>59811552.07</v>
+        <v>213215158.93000001</v>
       </c>
       <c r="H69" s="6">
-        <v>290136718.94</v>
+        <v>255209641.13999999</v>
       </c>
       <c r="I69" s="7">
-        <v>39067518.859999999</v>
+        <v>94481486.790000007</v>
       </c>
     </row>
     <row r="70" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -2868,7 +2856,7 @@
         <v>2026</v>
       </c>
       <c r="B70" s="4">
-        <v>1451</v>
+        <v>1631</v>
       </c>
       <c r="C70" s="5" t="s">
         <v>145</v>
@@ -2877,19 +2865,19 @@
         <v>146</v>
       </c>
       <c r="E70" s="6">
-        <v>2094010368.48</v>
+        <v>5434721.7300000004</v>
       </c>
       <c r="F70" s="6">
-        <v>1786140465.1500001</v>
+        <v>5239057.58</v>
       </c>
       <c r="G70" s="6">
-        <v>1741119589.71</v>
+        <v>5144290.3</v>
       </c>
       <c r="H70" s="6">
-        <v>1786140465.1500001</v>
+        <v>5239057.58</v>
       </c>
       <c r="I70" s="7">
-        <v>132690325.31999999</v>
+        <v>34378.25</v>
       </c>
     </row>
     <row r="71" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -2897,7 +2885,7 @@
         <v>2026</v>
       </c>
       <c r="B71" s="4">
-        <v>1371</v>
+        <v>2351</v>
       </c>
       <c r="C71" s="5" t="s">
         <v>147</v>
@@ -2906,19 +2894,19 @@
         <v>148</v>
       </c>
       <c r="E71" s="6">
-        <v>94039487.670000002</v>
+        <v>175928107.13999999</v>
       </c>
       <c r="F71" s="6">
-        <v>86994130.549999997</v>
+        <v>156353409.87</v>
       </c>
       <c r="G71" s="6">
-        <v>83230814.719999999</v>
+        <v>153454303.44999999</v>
       </c>
       <c r="H71" s="6">
-        <v>86994130.549999997</v>
+        <v>156353409.87</v>
       </c>
       <c r="I71" s="7">
-        <v>8157878.4699999997</v>
+        <v>16856020.100000001</v>
       </c>
     </row>
     <row r="72" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -2926,7 +2914,7 @@
         <v>2026</v>
       </c>
       <c r="B72" s="4">
-        <v>1501</v>
+        <v>2311</v>
       </c>
       <c r="C72" s="5" t="s">
         <v>149</v>
@@ -2935,109 +2923,22 @@
         <v>150</v>
       </c>
       <c r="E72" s="6">
-        <v>331698744.00999999</v>
+        <v>203725658.28</v>
       </c>
       <c r="F72" s="6">
-        <v>248622477.06999999</v>
+        <v>186502453.09</v>
       </c>
       <c r="G72" s="6">
-        <v>212593416.47999999</v>
+        <v>182726421.90000001</v>
       </c>
       <c r="H72" s="6">
-        <v>248622477.06999999</v>
+        <v>186502453.09</v>
       </c>
       <c r="I72" s="7">
-        <v>94481486.790000007</v>
-      </c>
-    </row>
-    <row r="73" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="4">
-        <v>2026</v>
-      </c>
-      <c r="B73" s="4">
-        <v>1631</v>
-      </c>
-      <c r="C73" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="D73" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="E73" s="6">
-        <v>5435087.3300000001</v>
-      </c>
-      <c r="F73" s="6">
-        <v>5239423.18</v>
-      </c>
-      <c r="G73" s="6">
-        <v>5134516.16</v>
-      </c>
-      <c r="H73" s="6">
-        <v>5239423.18</v>
-      </c>
-      <c r="I73" s="7">
-        <v>34378.25</v>
-      </c>
-    </row>
-    <row r="74" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="4">
-        <v>2026</v>
-      </c>
-      <c r="B74" s="4">
-        <v>2351</v>
-      </c>
-      <c r="C74" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="D74" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="E74" s="6">
-        <v>175919781.74000001</v>
-      </c>
-      <c r="F74" s="6">
-        <v>155436772.13</v>
-      </c>
-      <c r="G74" s="6">
-        <v>152690616.86000001</v>
-      </c>
-      <c r="H74" s="6">
-        <v>155436772.13</v>
-      </c>
-      <c r="I74" s="7">
-        <v>16856020.100000001</v>
-      </c>
-    </row>
-    <row r="75" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="4">
-        <v>2026</v>
-      </c>
-      <c r="B75" s="4">
-        <v>2311</v>
-      </c>
-      <c r="C75" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="D75" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="E75" s="6">
-        <v>203328487.56</v>
-      </c>
-      <c r="F75" s="6">
-        <v>185439100.47</v>
-      </c>
-      <c r="G75" s="6">
-        <v>181658842.28</v>
-      </c>
-      <c r="H75" s="6">
-        <v>185439100.47</v>
-      </c>
-      <c r="I75" s="7">
-        <v>21478429.68</v>
-      </c>
-    </row>
-    <row r="76" spans="1:9" s="1" customFormat="1" ht="28.7" customHeight="1" x14ac:dyDescent="0.2"/>
+        <v>21512236.109999999</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" s="1" customFormat="1" ht="28.7" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait"/>
